--- a/01_analyses_states/Chandigarh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Chandigarh/results/SoIB_summaries.xlsx
@@ -461,7 +461,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C8">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>0</v>

--- a/01_analyses_states/Chandigarh/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Chandigarh/results/SoIB_summaries.xlsx
@@ -398,6 +398,9 @@
       <c r="C2">
         <v>0</v>
       </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -411,6 +414,9 @@
       <c r="C3">
         <v>0</v>
       </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,7 +428,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -437,6 +446,9 @@
       <c r="C5">
         <v>0</v>
       </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -450,6 +462,9 @@
       <c r="C6">
         <v>0</v>
       </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,7 +476,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -471,10 +486,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="C8">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -603,7 +618,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +628,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +665,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3">
@@ -673,10 +688,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -733,16 +748,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2">
-        <v>85.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E2">
-        <v>87.09999999999999</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="3">
@@ -752,16 +767,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>14.6</v>
+        <v>12.6</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>12.9</v>
+        <v>11.8</v>
       </c>
     </row>
   </sheetData>
